--- a/output/pdf_financials_xlsx/SKEL.xlsx
+++ b/output/pdf_financials_xlsx/SKEL.xlsx
@@ -5839,46 +5839,46 @@
         <v>0.187304</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.187304</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.187304</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.187304</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.187304</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.333519</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.38789</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.586125</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.586125</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.586125</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.586125</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.726855</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.726855</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.726855</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.726855</v>
       </c>
     </row>
     <row r="93">
@@ -7295,13 +7295,13 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.320654</v>
+        <v>-0.5821769999999999</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.634386</v>
+        <v>0.597955</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.684206</v>
+        <v>0.688263</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0.040179</v>
@@ -7313,19 +7313,19 @@
         <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.129359</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.384281</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.8152199999999999</v>
+        <v>0.677714</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>-0.031041</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.028293</v>
       </c>
       <c r="O118" s="3" t="n">
         <v>0.347286</v>
@@ -9248,7 +9248,11 @@
           <t>Share-based payment reserve 6,7,8</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -9822,7 +9826,11 @@
           <t>Share-based payment reserve 6,7,8</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10305,7 +10313,11 @@
           <t>Share-based payment reserve 6,7,8</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11049,7 +11061,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12158,7 +12174,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -12455,7 +12475,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -13051,7 +13075,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -13247,7 +13275,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -17228,7 +17260,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -23171,7 +23207,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -23268,7 +23308,11 @@
           <t>Recovery of exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SKEL.xlsx
+++ b/output/pdf_financials_xlsx/SKEL.xlsx
@@ -1032,13 +1032,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001057</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005092</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000413</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>-0.03221</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.40257</v>
+        <v>-0.403627</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.7120610000000001</v>
+        <v>-0.717153</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.127468</v>
+        <v>-1.127881</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.01386</v>
@@ -2090,13 +2090,13 @@
         <v>-0.03221</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.40257</v>
+        <v>-0.403627</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.7120610000000001</v>
+        <v>-0.717153</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.127468</v>
+        <v>-1.127881</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.01386</v>
@@ -2394,55 +2394,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.253309</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.433911</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.103046</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.032484</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.02736</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.002703</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002423</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.332335</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.462874</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.500605</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.018026</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.644938</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.25016</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.979137</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.374516</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.215945</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.129265</v>
       </c>
     </row>
     <row r="35">
@@ -2510,55 +2510,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.253309</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.433911</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.103046</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.032484</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.02736</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.002703</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002423</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.332335</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.462874</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.500605</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.018026</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.644938</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.25016</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.979137</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.374516</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.215945</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.129265</v>
       </c>
     </row>
     <row r="37">
@@ -3206,55 +3206,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.253309</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.444628</v>
+        <v>0.010717</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.110635</v>
+        <v>0.007589</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.032944</v>
+        <v>0.00046</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.02782</v>
+        <v>0.00046</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.003163</v>
+        <v>0.00046</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.337999</v>
+        <v>0.005664</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.471351</v>
+        <v>0.008477</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.592432</v>
+        <v>0.09182700000000001</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.019612</v>
+        <v>0.001586</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.657999</v>
+        <v>0.013061</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.25016</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.021479</v>
+        <v>0.042342</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.387869</v>
+        <v>0.013353</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.215945</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.129265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -37509,7 +37509,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -42214,7 +42214,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -44113,7 +44113,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">

--- a/output/pdf_financials_xlsx/SKEL.xlsx
+++ b/output/pdf_financials_xlsx/SKEL.xlsx
@@ -739,13 +739,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.01919</v>
+        <v>0.02221</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.186497</v>
+        <v>0.215729</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.126879</v>
+        <v>0.188364</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.159589</v>
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.01919</v>
+        <v>0.02221</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.186497</v>
+        <v>0.215729</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.126879</v>
+        <v>0.188364</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.227395</v>
@@ -1319,16 +1319,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.010984</v>
+        <v>-0.010984</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.153443</v>
+        <v>-0.153443</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.1786</v>
+        <v>-0.1786</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.0141</v>
+        <v>-0.0141</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -23710,7 +23710,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -24114,7 +24118,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -25033,7 +25041,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E170" s="5" t="n">
         <v>-0.010984</v>
       </c>
@@ -42412,7 +42424,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -42511,7 +42527,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E346" s="5" t="n">
         <v>0.00302</v>
       </c>
@@ -43509,7 +43529,11 @@
           <t>Future income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -44319,7 +44343,11 @@
           <t>Future income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E364" s="5" t="n">
         <v>0.010984</v>
       </c>
